--- a/sales_dashboard_dataexel.xlsx
+++ b/sales_dashboard_dataexel.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sales_by_Year" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sales_by_Month" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sales_by_Sub_Category" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sales_by_Region" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Top_Products" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Bottom_Products" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Top_Sub_Products" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Bottom_Sub_Products" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="KPI_DATA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sales_by_Year" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sales_by_Month" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sales_by_Sub_Category" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sales_by_Region" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Top_Products" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Bottom_Products" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Top_Sub_Products" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Bottom_Sub_Products" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,51 +433,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>KPI</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2015</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total_Sales</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>2975599</v>
+        <v>14956982</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2016</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total_Orders</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>3131959</v>
+        <v>9994</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2017</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total_Profit</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>3871912</v>
+        <v>3747121.2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2018</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average_Order_Value</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>4977512</v>
+        <v>1496.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>General_Profit_Margin_%</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>25.05</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +509,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -507,98 +526,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2015</v>
       </c>
       <c r="B2" t="n">
-        <v>902128</v>
+        <v>2975599</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>2016</v>
       </c>
       <c r="B3" t="n">
-        <v>830301</v>
+        <v>3131959</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2017</v>
       </c>
       <c r="B4" t="n">
-        <v>1247196</v>
+        <v>3871912</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2018</v>
       </c>
       <c r="B5" t="n">
-        <v>1028352</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1251327</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1028694</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1107483</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1220430</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1706141</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1237389</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1794831</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1602710</v>
+        <v>4977512</v>
       </c>
     </row>
   </sheetData>
@@ -612,13 +567,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sub Category</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -628,233 +583,99 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Atta &amp; Flour</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>534649</v>
+        <v>902128</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Biscuits</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>684083</v>
+        <v>830301</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Breads &amp; Buns</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>742586</v>
+        <v>1247196</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cakes</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>685612</v>
+        <v>1028352</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chicken</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>520497</v>
+        <v>1251327</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Chocolates</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>733898</v>
+        <v>1028694</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cookies</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>768213</v>
+        <v>1107483</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Dals &amp; Pulses</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>523371</v>
+        <v>1220430</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Edible Oil &amp; Ghee</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>668086</v>
+        <v>1706141</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Eggs</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>575156</v>
+        <v>1237389</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fish</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>560548</v>
+        <v>1794831</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fresh Fruits</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>551212</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>525842</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Health Drinks</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1051439</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Masalas</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>697480</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Mutton</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>611200</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Noodles</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>735435</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Organic Fruits</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>503402</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Organic Staples</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>558929</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Organic Vegetables</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>520271</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Rice</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>498323</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Soft Drinks</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1033874</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Spices</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>672876</v>
+        <v>1602710</v>
       </c>
     </row>
   </sheetData>
@@ -868,13 +689,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Sub Category</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -886,51 +707,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Atta &amp; Flour</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3468156</v>
+        <v>534649</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Biscuits</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4248368</v>
+        <v>684083</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Breads &amp; Buns</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1254</v>
+        <v>742586</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Cakes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2440461</v>
+        <v>685612</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4798743</v>
+        <v>520497</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chocolates</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>733898</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cookies</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>768213</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dals &amp; Pulses</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>523371</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Edible Oil &amp; Ghee</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>668086</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Eggs</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>575156</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>560548</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fresh Fruits</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>551212</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>525842</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Health Drinks</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1051439</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Masalas</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>697480</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mutton</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>611200</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Noodles</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>735435</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Organic Fruits</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>503402</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Organic Staples</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>558929</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Organic Vegetables</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>520271</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>498323</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Soft Drinks</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1033874</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Spices</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>672876</v>
       </c>
     </row>
   </sheetData>
@@ -944,13 +945,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -962,71 +963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Eggs, Meat &amp; Fish</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2267401</v>
+        <v>3468156</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>East</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2237546</v>
+        <v>4248368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Food Grains</t>
+          <t>North</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2115272</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>South</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2112281</v>
+        <v>2440461</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fruits &amp; Veggies</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2100727</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2085313</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Oil &amp; Masala</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2038442</v>
+        <v>4798743</v>
       </c>
     </row>
   </sheetData>
@@ -1058,31 +1039,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Oil &amp; Masala</t>
+          <t>Eggs, Meat &amp; Fish</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2038442</v>
+        <v>2267401</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2085313</v>
+        <v>2237546</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fruits &amp; Veggies</t>
+          <t>Food Grains</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2100727</v>
+        <v>2115272</v>
       </c>
     </row>
     <row r="5">
@@ -1098,31 +1079,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Food Grains</t>
+          <t>Fruits &amp; Veggies</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2115272</v>
+        <v>2100727</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2237546</v>
+        <v>2085313</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eggs, Meat &amp; Fish</t>
+          <t>Oil &amp; Masala</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2267401</v>
+        <v>2038442</v>
       </c>
     </row>
   </sheetData>
@@ -1136,13 +1117,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sub Category</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1154,231 +1135,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Health Drinks</t>
+          <t>Oil &amp; Masala</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1051439</v>
+        <v>2038442</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Soft Drinks</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1033874</v>
+        <v>2085313</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cookies</t>
+          <t>Fruits &amp; Veggies</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>768213</v>
+        <v>2100727</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Breads &amp; Buns</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>742586</v>
+        <v>2112281</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Noodles</t>
+          <t>Food Grains</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>735435</v>
+        <v>2115272</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chocolates</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>733898</v>
+        <v>2237546</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Masalas</t>
+          <t>Eggs, Meat &amp; Fish</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>697480</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cakes</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>685612</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Biscuits</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>684083</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Spices</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>672876</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Edible Oil &amp; Ghee</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>668086</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Mutton</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>611200</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Eggs</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>575156</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fish</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>560548</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Organic Staples</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>558929</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fresh Fruits</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>551212</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Atta &amp; Flour</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>534649</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fresh Vegetables</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>525842</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Dals &amp; Pulses</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>523371</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Chicken</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>520497</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Organic Vegetables</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>520271</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Organic Fruits</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>503402</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Rice</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>498323</v>
+        <v>2267401</v>
       </c>
     </row>
   </sheetData>
@@ -1410,6 +1231,262 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Health Drinks</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1051439</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Soft Drinks</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1033874</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cookies</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>768213</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Breads &amp; Buns</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>742586</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Noodles</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>735435</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chocolates</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>733898</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Masalas</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>697480</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cakes</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>685612</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Biscuits</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>684083</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Spices</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>672876</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Edible Oil &amp; Ghee</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>668086</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mutton</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>611200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Eggs</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>575156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>560548</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Organic Staples</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>558929</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fresh Fruits</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>551212</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Atta &amp; Flour</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>534649</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fresh Vegetables</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>525842</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dals &amp; Pulses</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>523371</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>520497</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Organic Vegetables</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>520271</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Organic Fruits</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>503402</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>498323</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Rice</t>
         </is>
       </c>
